--- a/Data/Submission/capitals_enriched_ВоленбовськийГВ.xlsx
+++ b/Data/Submission/capitals_enriched_ВоленбовськийГВ.xlsx
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>

--- a/Data/Submission/capitals_enriched_ВоленбовськийГВ.xlsx
+++ b/Data/Submission/capitals_enriched_ВоленбовськийГВ.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="enrichment_log" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="звірка_з_еталоном" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,10 +419,10 @@
           <t>France</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="0" t="n">
         <v>2023</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="0" t="n">
         <v>2364</v>
       </c>
     </row>
@@ -446,10 +447,10 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="0" t="n">
         <v>1434</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="0" t="n">
         <v>1839</v>
       </c>
     </row>
@@ -474,10 +475,10 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="0" t="n">
         <v>876</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="0" t="n">
         <v>1050</v>
       </c>
     </row>
@@ -502,10 +503,10 @@
           <t>Austria</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="0" t="n">
         <v>524</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="0" t="n">
         <v>680</v>
       </c>
     </row>
@@ -530,10 +531,10 @@
           <t>Ukraine</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="0" t="n">
         <v>689</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="0" t="n">
         <v>778</v>
       </c>
     </row>
@@ -558,10 +559,10 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="0" t="n">
         <v>1363</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="0" t="n">
         <v>1948</v>
       </c>
     </row>
@@ -586,10 +587,10 @@
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="0" t="n">
         <v>503</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="0" t="n">
         <v>629</v>
       </c>
     </row>
@@ -614,10 +615,10 @@
           <t>Hungary</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="0" t="n">
         <v>214</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="0" t="n">
         <v>244</v>
       </c>
     </row>
@@ -642,10 +643,10 @@
           <t>Norway</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="0" t="n">
         <v>417</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="0" t="n">
         <v>531</v>
       </c>
     </row>
@@ -670,10 +671,10 @@
           <t>Turkey</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="0" t="n">
         <v>561</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="0" t="n">
         <v>1092</v>
       </c>
     </row>
@@ -1749,523 +1750,835 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>distance</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>km</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>geo_distance</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q1899 ; http://www.wikidata.org/entity/Q90</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>haversine(Kyiv, Paris)</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 2364 км</t>
+        </is>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>distance</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>1434</v>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>km</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>geo_distance</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q84 ; http://www.wikidata.org/entity/Q220</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>haversine(London, Rome)</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 1839 км</t>
+        </is>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>distance</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>876</v>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>km</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>geo_distance</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q90 ; http://www.wikidata.org/entity/Q64</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>haversine(Paris, Berlin)</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
+        <is>
+          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 1050 км</t>
+        </is>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>76</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>distance</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>524</v>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>km</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>geo_distance</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q64 ; http://www.wikidata.org/entity/Q1741</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>haversine(Berlin, Vienna)</t>
+        </is>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="inlineStr">
+        <is>
+          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 680 км</t>
+        </is>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>distance</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>689</v>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>km</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>geo_distance</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q270 ; http://www.wikidata.org/entity/Q1899</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>haversine(Warsaw, Kyiv)</t>
+        </is>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 778 км</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>distance</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>1363</v>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>km</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>geo_distance</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q220 ; http://www.wikidata.org/entity/Q2807</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>haversine(Rome, Madrid)</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 1948 км</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>distance</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>503</v>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>km</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>geo_distance</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q2807 ; http://www.wikidata.org/entity/Q597</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>haversine(Madrid, Lisbon)</t>
+        </is>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 629 км</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>distance</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>214</v>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>km</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>geo_distance</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q1741 ; http://www.wikidata.org/entity/Q1781</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>haversine(Vienna, Budapest)</t>
+        </is>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 244 км</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="L9" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>distance</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>417</v>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>km</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>geo_distance</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q1754 ; http://www.wikidata.org/entity/Q585</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>haversine(Stockholm, Oslo)</t>
+        </is>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 531 км</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="L10" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>distance</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>561</v>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>km</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>geo_distance</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q1524 ; http://www.wikidata.org/entity/Q406</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>haversine(Athens, Istanbul)</t>
+        </is>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 1092 км</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="L11" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="4" min="1" max="1"/>
+    <col width="12" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16" customWidth="1" style="4" min="3" max="3"/>
+    <col width="15" customWidth="1" style="4" min="4" max="4"/>
+    <col width="16" customWidth="1" style="4" min="5" max="5"/>
+    <col width="46" customWidth="1" style="4" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>рядок</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>еталон</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>наше значення</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>відхилення, %</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>distance_road</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>вердикт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="n">
         <v>2</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>distance</t>
-        </is>
+      <c r="B2" t="n">
+        <v>2500</v>
       </c>
       <c r="C2" t="n">
         <v>2023</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>km</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>geo_distance</t>
-        </is>
+      <c r="D2" t="n">
+        <v>-19.1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q1899 ; http://www.wikidata.org/entity/Q90</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>haversine(Kyiv, Paris)</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 2364 км</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>68</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
+          <t>еталон відповідає колонці distance_road</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>3</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>distance</t>
-        </is>
+      <c r="B3" t="n">
+        <v>1435</v>
       </c>
       <c r="C3" t="n">
         <v>1434</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>km</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>geo_distance</t>
-        </is>
+      <c r="D3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1839</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q84 ; http://www.wikidata.org/entity/Q220</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>haversine(London, Rome)</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 1839 км</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>70</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
+          <t>у допуску</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>4</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>distance</t>
-        </is>
+      <c r="B4" t="n">
+        <v>878</v>
       </c>
       <c r="C4" t="n">
         <v>876</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>km</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>geo_distance</t>
-        </is>
+      <c r="D4" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1050</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q90 ; http://www.wikidata.org/entity/Q64</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>haversine(Paris, Berlin)</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 1050 км</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>76</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
+          <t>у допуску</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>5</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>distance</t>
-        </is>
+      <c r="B5" t="n">
+        <v>779</v>
       </c>
       <c r="C5" t="n">
         <v>524</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>km</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>geo_distance</t>
-        </is>
+      <c r="D5" t="n">
+        <v>-32.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>680</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q64 ; http://www.wikidata.org/entity/Q1741</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>haversine(Berlin, Vienna)</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 680 км</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>67</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
+          <t>поза допуском</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>6</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>distance</t>
-        </is>
+      <c r="B6" t="n">
+        <v>688</v>
       </c>
       <c r="C6" t="n">
         <v>689</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>km</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>geo_distance</t>
-        </is>
+      <c r="D6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>778</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q270 ; http://www.wikidata.org/entity/Q1899</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>haversine(Warsaw, Kyiv)</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 778 км</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>75</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
+          <t>у допуску</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>7</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>distance</t>
-        </is>
+      <c r="B7" t="n">
+        <v>1363</v>
       </c>
       <c r="C7" t="n">
         <v>1363</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>km</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>geo_distance</t>
-        </is>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1948</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q220 ; http://www.wikidata.org/entity/Q2807</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>haversine(Rome, Madrid)</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 1948 км</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>78</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
+          <t>у допуску</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>8</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>distance</t>
-        </is>
+      <c r="B8" t="n">
+        <v>502</v>
       </c>
       <c r="C8" t="n">
         <v>503</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>km</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>geo_distance</t>
-        </is>
+      <c r="D8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>629</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q2807 ; http://www.wikidata.org/entity/Q597</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>haversine(Madrid, Lisbon)</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 629 км</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>69</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
+          <t>у допуску</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>9</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>distance</t>
-        </is>
+      <c r="B9" t="n">
+        <v>243</v>
       </c>
       <c r="C9" t="n">
         <v>214</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>km</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>geo_distance</t>
-        </is>
+      <c r="D9" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>244</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q1741 ; http://www.wikidata.org/entity/Q1781</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>haversine(Vienna, Budapest)</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 244 км</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>73</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
+          <t>еталон відповідає колонці distance_road</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>10</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>distance</t>
-        </is>
+      <c r="B10" t="n">
+        <v>416</v>
       </c>
       <c r="C10" t="n">
         <v>417</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>km</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>geo_distance</t>
-        </is>
+      <c r="D10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>531</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q1754 ; http://www.wikidata.org/entity/Q585</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>haversine(Stockholm, Oslo)</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 531 км</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>14</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
+          <t>у допуску</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>11</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>distance</t>
-        </is>
+      <c r="B11" t="n">
+        <v>563</v>
       </c>
       <c r="C11" t="n">
         <v>561</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>km</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>geo_distance</t>
-        </is>
+      <c r="D11" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1092</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q1524 ; http://www.wikidata.org/entity/Q406</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>haversine(Athens, Istanbul)</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>[geo_distance] Велике коло за координатами Wikidata; автомобільний маршрут OSRM 1092 км</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>13</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
+          <t>у допуску</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>У допуску ±10%</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7 з 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>З урахуванням другого трактування</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>9 з 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Пояснення: у завданні сказано «пряма відстань», тому основна колонка це велике коло за координатами Wikidata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Рядки, де еталон розходиться, відповідають відстані дорогами (перевірено маршрутизатором OSRM) або не збігаються з жодним визначенням (Берлін-Відень 779 при прямій 524 і дорозі 680).</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Data/Submission/capitals_enriched_ВоленбовськийГВ.xlsx
+++ b/Data/Submission/capitals_enriched_ВоленбовськийГВ.xlsx
@@ -1672,20 +1672,6 @@
   </sheetPr>
   <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" style="4" min="1" max="1"/>
-    <col width="16" customWidth="1" style="4" min="2" max="2"/>
-    <col width="12" customWidth="1" style="4" min="3" max="3"/>
-    <col width="8" customWidth="1" style="4" min="4" max="4"/>
-    <col width="20" customWidth="1" style="4" min="5" max="5"/>
-    <col width="46" customWidth="1" style="4" min="6" max="6"/>
-    <col width="40" customWidth="1" style="4" min="7" max="7"/>
-    <col width="8" customWidth="1" style="4" min="8" max="8"/>
-    <col width="14" customWidth="1" style="4" min="9" max="9"/>
-    <col width="60" customWidth="1" style="4" min="10" max="10"/>
-    <col width="12" customWidth="1" style="4" min="11" max="11"/>
-    <col width="10" customWidth="1" style="4" min="12" max="12"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
@@ -1795,7 +1781,7 @@
         </is>
       </c>
       <c r="K2" s="0" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="L2" s="0" t="n">
         <v>0</v>
@@ -1847,7 +1833,7 @@
         </is>
       </c>
       <c r="K3" s="0" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L3" s="0" t="n">
         <v>0</v>
@@ -1899,7 +1885,7 @@
         </is>
       </c>
       <c r="K4" s="0" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="L4" s="0" t="n">
         <v>0</v>
@@ -1951,7 +1937,7 @@
         </is>
       </c>
       <c r="K5" s="0" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="L5" s="0" t="n">
         <v>0</v>
@@ -2003,7 +1989,7 @@
         </is>
       </c>
       <c r="K6" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L6" s="0" t="n">
         <v>0</v>
@@ -2055,7 +2041,7 @@
         </is>
       </c>
       <c r="K7" s="0" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="L7" s="0" t="n">
         <v>0</v>
@@ -2107,7 +2093,7 @@
         </is>
       </c>
       <c r="K8" s="0" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="L8" s="0" t="n">
         <v>0</v>
@@ -2159,7 +2145,7 @@
         </is>
       </c>
       <c r="K9" s="0" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="L9" s="0" t="n">
         <v>0</v>
@@ -2211,7 +2197,7 @@
         </is>
       </c>
       <c r="K10" s="0" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L10" s="0" t="n">
         <v>0</v>
@@ -2263,7 +2249,7 @@
         </is>
       </c>
       <c r="K11" s="0" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L11" s="0" t="n">
         <v>0</v>
